--- a/test_result_gui.xlsx
+++ b/test_result_gui.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,6 +523,61 @@
         </is>
       </c>
       <c r="K2" t="inlineStr">
+        <is>
+          <t>не завершено</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>20144111</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ПОМОРЦЕВА ТАТЬЯНА ВИКТОРОВНА</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://old.bankrot.fedresurs.ru/PrivatePersonCard.aspx?ID=79E629216865D8FA3DC4F892C7650F44</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>О признании гражданина банкротом и введении реализации имущества гражданина</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>А33-29318/2025</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Касимова (ранее Казакова) Алина Григорьевна</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>603000, г. Нижний Новгород, а/я 680</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10.02.2026</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>663951, с. Гмирянка, Красноярский край, ул. Лесная, 15</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>не завершено</t>
         </is>
